--- a/シルバー人材センター_業務依頼書.xlsx
+++ b/シルバー人材センター_業務依頼書.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'業務内容'!$A$1:$C$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'チェックリスト'!$A$1:$F$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'チェックリスト'!$A$1:$F$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -615,7 +615,11 @@
           <t>氏名</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr"/>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>背古</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="B9" s="6" t="inlineStr">
@@ -645,7 +649,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>マンション（　　階）　・　戸建て　／　間取り（　　　　）</t>
+          <t>マンション（　　階）　・　戸建て　／　間取り：1LDK</t>
         </is>
       </c>
     </row>
@@ -669,15 +673,16 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
+    <row r="15" ht="32" customHeight="1">
       <c r="B15" s="6" t="inlineStr">
         <is>
           <t>希望曜日・時間帯</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　曜日　　　時　　分 〜　　時　　分</t>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>火曜日 10:00〜12:00
+（難しい場合は、会員の方のご都合のよい曜日・時間に合わせます）</t>
         </is>
       </c>
     </row>
@@ -689,19 +694,19 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>1回あたり2時間程度を想定（作業量に応じてご相談させてください）</t>
+          <t>1回2時間</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>開始希望日</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　月　　日ごろ</t>
+          <t>開始希望</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>11月募集でお願いします</t>
         </is>
       </c>
     </row>
@@ -731,7 +736,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="66" customHeight="1">
+    <row r="21" ht="50" customHeight="1">
       <c r="B21" s="6" t="inlineStr">
         <is>
           <t>（2）2週に1回</t>
@@ -739,14 +744,13 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>・敷きパッドの洗濯（夏場は毎回）
-・掛け布団カバーの洗濯
+          <t>・シーツ類（敷きパッドなど）の洗濯
 ・浴室の掃除
 ・玄関の掃き掃除・たたきの拭き掃除</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="66" customHeight="1">
+    <row r="22" ht="36" customHeight="1">
       <c r="B22" s="6" t="inlineStr">
         <is>
           <t>（3）月1回</t>
@@ -754,10 +758,8 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>・靴洗い
-・掛け布団・敷布団の天日干し（晴天時のみ）
-・冷蔵庫の中の整理と拭き掃除
-・エアコンフィルターの掃除（使う季節のみ）</t>
+          <t>・靴磨き（靴クリームで磨くのみ。洗う必要はありません）
+・冷蔵庫の中の整理と拭き掃除</t>
         </is>
       </c>
     </row>
@@ -837,25 +839,26 @@
     <row r="33" ht="22" customHeight="1">
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>6. 事前に確認させていただきたいこと</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="66" customHeight="1">
+          <t>6. 確認済みの事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="82" customHeight="1">
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>・料金（1時間あたりの料金、最低利用時間、交通費など）とお支払い方法
-・上記の作業内容で、お引き受けいただけない作業があるかどうか
-・掛け布団の洗濯が可能かどうか（難しい場合は天日干しとカバーの洗濯のみで結構です）
-・ご契約までの流れ（会員登録、事前の打ち合わせ・下見など）</t>
+          <t>・料金：1回2時間 3,105円（配分金2,736円＋事務手数料13％＋交通費14円）
+・会員紹介の流れ：月1回の募集 → 会員応募 → 自宅での面談（道具・洗剤と作業量の確認）
+・会員が見つからない場合もあることを了承しています
+・布団はないため、布団の洗濯・干す作業はありません（シーツ類の洗濯のみ）
+・エアコンフィルターの掃除は依頼者が行います</t>
         </is>
       </c>
     </row>
     <row r="35" ht="6" customHeight="1"/>
-    <row r="36" ht="30" customHeight="1">
+    <row r="36" ht="20" customHeight="1">
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>お手数をおかけしますが、ご確認のうえご連絡いただけますと幸いです。何卒よろしくお願い申し上げます。</t>
+          <t>お手数をおかけしますが、何卒よろしくお願い申し上げます。</t>
         </is>
       </c>
     </row>
@@ -866,7 +869,11 @@
           <t>依頼者氏名</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr"/>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>背古</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="6" t="inlineStr">
@@ -908,7 +915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1081,7 +1088,7 @@
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>敷きパッド洗濯（夏は毎回）</t>
+          <t>シーツ類（敷きパッドなど）の洗濯</t>
         </is>
       </c>
       <c r="B13" s="14" t="n"/>
@@ -1105,7 +1112,7 @@
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>掛け布団カバー洗濯</t>
+          <t>浴室の掃除</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -1129,7 +1136,7 @@
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>浴室の掃除</t>
+          <t>玄関の掃除</t>
         </is>
       </c>
       <c r="B15" s="14" t="n"/>
@@ -1150,49 +1157,57 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>玄関の掃除</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>【月1回】</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>靴磨き（クリームで磨くのみ）</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>靴洗い</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="n"/>
+          <t>冷蔵庫の整理・拭き掃除</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
           <t>—</t>
@@ -1203,49 +1218,29 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="E18" s="14" t="n"/>
       <c r="F18" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>布団の天日干し（晴天時）</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="n"/>
-      <c r="D19" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E19" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>【季節ごと】</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="12" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>冷蔵庫の整理・拭き掃除</t>
+          <t>窓・網戸／カーテン</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
@@ -1258,50 +1253,34 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D20" s="14" t="n"/>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>エアコンフィルター（季節）</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E21" s="14" t="n"/>
-      <c r="F21" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
+      <c r="F20" s="14" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>作業員サイン</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="12" t="n"/>
+    </row>
+    <row r="22" ht="70" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>【季節ごと】</t>
+          <t>連絡事項</t>
         </is>
       </c>
       <c r="B22" s="12" t="n"/>
@@ -1310,60 +1289,8 @@
       <c r="E22" s="12" t="n"/>
       <c r="F22" s="12" t="n"/>
     </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>窓・網戸／カーテン</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C23" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D23" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="n"/>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>作業員サイン</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
-    </row>
-    <row r="25" ht="70" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>連絡事項</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="12" t="n"/>
-      <c r="F25" s="12" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>※第5週がない月は第5週の欄は使いません。季節ごとの作業は依頼者と相談のうえ行ってください。</t>
         </is>
@@ -1372,12 +1299,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A26:F26"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.6" right="0.6" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
